--- a/order_forms/006_raffle_ticket_generation_form--order_forms.xlsx
+++ b/order_forms/006_raffle_ticket_generation_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raffle_ticket_generation_form_page_1</t>
+          <t>event_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>raffle_ticket_generation_form_page_1_label</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>raffle_ticket_generation_form_page_1</t>
+          <t>ticket_price</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>raffle_ticket_generation_form_page_1_label</t>
+          <t>Ticket Price</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>event_name</t>
+          <t>ticket_quantity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>event_name_label</t>
+          <t>Ticket Quantity</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ticket_price</t>
+          <t>ticket_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ticket_price_label</t>
+          <t>Ticket Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ticket_quantity</t>
+          <t>order_notes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ticket_quantity_label</t>
+          <t>Order Notes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ticket_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ticket_type_label</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ticket_type</t>
+          <t>order_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ticket_type_label</t>
+          <t>Order Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>order_notes</t>
+          <t>contact_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>order_notes_label</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>order_comments</t>
+          <t>order_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>order_comments_label</t>
+          <t>Order Phone</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,159 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>order_comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>payment_method_label</t>
+          <t>Order Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>payment_method_label</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>order_email</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>order_email_label</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>contact_number_label</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>order_phone</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>order_phone_label</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>order_notes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>order_notes_label</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>order_comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>order_comments_label</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -891,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ticket_a',_'value':_'ticket_a'}</t>
+          <t>ticket_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Ticket A', 'value': 'ticket_a'}</t>
+          <t>Ticket A</t>
         </is>
       </c>
     </row>
@@ -941,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ticket_b',_'value':_'ticket_b'}</t>
+          <t>ticket_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Ticket B', 'value': 'ticket_b'}</t>
+          <t>Ticket B</t>
         </is>
       </c>
     </row>
@@ -958,131 +820,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ticket_c',_'value':_'ticket_c'}</t>
+          <t>ticket_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Ticket C', 'value': 'ticket_c'}</t>
+          <t>Ticket C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ticket_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'ticket_a',_'value':_'ticket_a'}</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Ticket A', 'value': 'ticket_a'}</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ticket_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'ticket_b',_'value':_'ticket_b'}</t>
+          <t>offline_payment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Ticket B', 'value': 'ticket_b'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ticket_type_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'ticket_c',_'value':_'ticket_c'}</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Ticket C', 'value': 'ticket_c'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'online_payment',_'value':_'online_payment'}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Online Payment', 'value': 'online_payment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'offline_payment',_'value':_'offline_payment'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Offline Payment', 'value': 'offline_payment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'online_payment',_'value':_'online_payment'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Online Payment', 'value': 'online_payment'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'offline_payment',_'value':_'offline_payment'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Offline Payment', 'value': 'offline_payment'}</t>
+          <t>Offline Payment</t>
         </is>
       </c>
     </row>
